--- a/output/full_scan/batch_seq8_2026-10-07.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-07.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7703</v>
+        <v>6944</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>828.4844592651032</v>
+        <v>1159.62472461368</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>206</v>
+        <v>908</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.58709865931338</v>
+        <v>82.17252085605793</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.53646841027022</v>
+        <v>29.16037435659837</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.7135521308993774</v>
+        <v>4.062472461367964</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.048522946026198</v>
+        <v>19.66262893617928</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7730</v>
+        <v>6862</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>807.6874053229274</v>
+        <v>1005.558520474028</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>195.5</v>
+        <v>148.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.93377396152515</v>
+        <v>62.41452347480213</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.72309316057849</v>
+        <v>17.50014764908173</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.470627660503602</v>
+        <v>3.780047099574414</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.136392696731037</v>
+        <v>1.357313264919766</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6862</v>
+        <v>7730</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>755.5585204740298</v>
+        <v>977.6874053229274</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.5</v>
+        <v>195.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.41452367684519</v>
+        <v>64.93377400369297</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.50014774957907</v>
+        <v>30.72309318594057</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.780047099574414</v>
+        <v>2.470627660503602</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.357313262583065</v>
+        <v>2.136392696063439</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6944</v>
+        <v>8021</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>744.6247246136796</v>
+        <v>919.70499207378</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>908</v>
+        <v>556</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>82.17252088457263</v>
+        <v>72.84195065683852</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.16037442404493</v>
+        <v>23.23251436400527</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.062472461367964</v>
+        <v>1.353879079027023</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>19.66262893039318</v>
+        <v>9.995641433732288</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6870</v>
+        <v>7795</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>739.5832759957647</v>
+        <v>893.3974230108604</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>316</v>
+        <v>545</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>54.9146380602844</v>
+        <v>57.14478109967065</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32.9750530789777</v>
+        <v>21.11221562410841</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4583518220535033</v>
+        <v>0.6435763043726754</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.134565896351463</v>
+        <v>6.537970538181478</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6933</v>
+        <v>7703</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>722.555551276664</v>
+        <v>868.4844592651032</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>385.5</v>
+        <v>206</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>64.86151839164506</v>
+        <v>63.58709885930268</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45.55361172961483</v>
+        <v>32.53646843000941</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5589329590917941</v>
+        <v>0.7135521308993774</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.8101905561933904</v>
+        <v>-0.0485229451360424</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7751</v>
+        <v>6983</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>722.2108215200061</v>
+        <v>864.0874315726818</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1600</v>
+        <v>382</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.25117252233318</v>
+        <v>67.1411208553163</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.52451974788308</v>
+        <v>29.85831382289009</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9655021519225891</v>
+        <v>6.432863712252131</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.95927901494845</v>
+        <v>2.704779166238863</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7792</v>
+        <v>6933</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>713.5561375639294</v>
+        <v>852.555551276664</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>406.5</v>
+        <v>385.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.07487904140761</v>
+        <v>64.86151841158478</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>56.5469876355708</v>
+        <v>45.55361172961483</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.196128861277584</v>
+        <v>0.5589329590917941</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.036407084084409</v>
+        <v>-0.810190556527175</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6859</v>
+        <v>7736</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>706.3665031647014</v>
+        <v>816.3980748663101</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>120.5</v>
+        <v>71.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.03150276348829</v>
+        <v>64.85912657350977</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40.59560193924384</v>
+        <v>25.8077818660034</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5456972254448345</v>
+        <v>1.739807486631016</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1734093717767098</v>
+        <v>0.3859085368132868</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7736</v>
+        <v>7711</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>701.3980748663101</v>
+        <v>808.7256343121639</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>71.8</v>
+        <v>632</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.85912658644499</v>
+        <v>63.26174636313712</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.8077818660034</v>
+        <v>29.83130614119309</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.739807486631016</v>
+        <v>0.7871399339291157</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3859085373028696</v>
+        <v>4.492464618711207</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7744</v>
+        <v>6988</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>688.6771477729756</v>
+        <v>782.0514650261206</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>533</v>
+        <v>12.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.91413514271891</v>
+        <v>63.72891755057216</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.53161096132361</v>
+        <v>14.42628165745702</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4143357957725497</v>
+        <v>1.901159036806604</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.044984415580466</v>
+        <v>0.1101854741155051</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6983</v>
+        <v>6870</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>674.0874315726818</v>
+        <v>779.5832759957647</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>382</v>
+        <v>316</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>67.14112090019728</v>
+        <v>54.91463814795066</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.8583138175173</v>
+        <v>32.97505309198901</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.432863712252131</v>
+        <v>0.4583518220535033</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.704779164347203</v>
+        <v>-2.134565898131783</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8028</v>
+        <v>6913</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>655.4673939951892</v>
+        <v>772.403144298588</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.01839512206761</v>
+        <v>52.50550158119091</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.15563430589323</v>
+        <v>15.71399170665159</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.054035143140038</v>
+        <v>2.120903942335504</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.889383979842814</v>
+        <v>0.6862401460870409</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6894</v>
+        <v>7751</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>654.680242534634</v>
+        <v>762.2108215200061</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>363</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.24901640628788</v>
+        <v>55.25117255397089</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.64063312290959</v>
+        <v>14.52451974530567</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8462903519878081</v>
+        <v>0.9655021519225891</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.9828411624590156</v>
+        <v>12.95927901350201</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7711</v>
+        <v>7712</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>638.7256343121639</v>
+        <v>758.7258156099915</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>632</v>
+        <v>173</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.26174623521363</v>
+        <v>64.38506042955919</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29.83130610914053</v>
+        <v>29.89984438730699</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7871399339291157</v>
+        <v>0.9594430473719616</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.492464625053664</v>
+        <v>1.559293704257586</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6861</v>
+        <v>7792</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>629.5511765085317</v>
+        <v>753.5561375639294</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>270.5</v>
+        <v>406.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.47307096932728</v>
+        <v>62.0748790859319</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>38.6935759265417</v>
+        <v>56.54698764372576</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4057739935233445</v>
+        <v>2.196128861277584</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.949999915909629</v>
+        <v>3.036407081525169</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6913</v>
+        <v>7788</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>617.403144298588</v>
+        <v>747.8041784865881</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>134</v>
+        <v>329</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.50550153951755</v>
+        <v>58.43755486602988</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.71399164790781</v>
+        <v>22.01056461070159</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.120903942335504</v>
+        <v>2.135001913144483</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6862401468659618</v>
+        <v>4.165771182041524</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8021</v>
+        <v>6861</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>614.7049920737802</v>
+        <v>729.5511765085316</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>556</v>
+        <v>270.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>72.84195066647185</v>
+        <v>57.47307096751577</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.23251432324348</v>
+        <v>38.69357592723238</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.353879079027023</v>
+        <v>0.4057739935233445</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>9.99564143284212</v>
+        <v>1.949999915776114</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7795</v>
+        <v>7744</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>613.3974230108604</v>
+        <v>728.6771477729754</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.14478107628798</v>
+        <v>55.9141347426556</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.11221557808972</v>
+        <v>26.53161088729641</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6435763043726754</v>
+        <v>0.4143357957725497</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>6.537970538181478</v>
+        <v>-1.044984405232246</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6988</v>
+        <v>6953</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>612.0514650261206</v>
+        <v>724.7526776605492</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12.85</v>
+        <v>257</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.72891710904581</v>
+        <v>64.8888554107711</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.42628132640816</v>
+        <v>22.55459642540777</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.901159036806604</v>
+        <v>0.7752677660549195</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1101854743491764</v>
+        <v>2.076534444498339</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7799</v>
+        <v>6957</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>610.1277284248151</v>
+        <v>700.5426938786937</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>516</v>
+        <v>444</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.52493732982525</v>
+        <v>88.09248767902263</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45.79094341306903</v>
+        <v>56.66546891380062</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6055597024779665</v>
+        <v>1.209779693106451</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.6062826307413545</v>
+        <v>14.18511483120432</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6885</v>
+        <v>6894</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>603.0646349000027</v>
+        <v>694.680242534634</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>30.4</v>
+        <v>363</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.42290324022962</v>
+        <v>55.24901644421748</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>54.25861053511873</v>
+        <v>28.64063296843925</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9759503290424624</v>
+        <v>0.8462903519878081</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.2718839591010109</v>
+        <v>-0.982841161791474</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6937</v>
+        <v>6859</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>602.3105510449607</v>
+        <v>676.3665031647012</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>292.5</v>
+        <v>120.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>49.58284775222983</v>
+        <v>56.03150266067643</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.11098727474073</v>
+        <v>40.59560201429397</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6202836648013386</v>
+        <v>0.5456972254448345</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.199343950378801</v>
+        <v>-0.173409371109086</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7788</v>
+        <v>7810</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>587.8041784865881</v>
+        <v>666.4541579356874</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>329</v>
+        <v>248.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.43755483404222</v>
+        <v>69.7184898982045</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22.01056447122511</v>
+        <v>37.36272824564839</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.135001913144483</v>
+        <v>0.9330418095833964</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4.165771182931678</v>
+        <v>2.112840732294385</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7712</v>
+        <v>7556</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>578.7258156099916</v>
+        <v>660.5677967067695</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>173</v>
+        <v>283</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64.38506026217298</v>
+        <v>62.20017776894414</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.89984435218891</v>
+        <v>33.89043032335272</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9594430473719616</v>
+        <v>2.199991520531728</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.55929370470266</v>
+        <v>3.355133063519518</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6953</v>
+        <v>8028</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>569.7526776605491</v>
+        <v>655.4673939951892</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>64.8888554107711</v>
+        <v>63.01839513091682</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.55459641667228</v>
+        <v>27.15563430589323</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7752677660549195</v>
+        <v>1.054035143140038</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.07653444438705</v>
+        <v>3.889383979731504</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6869</v>
+        <v>7749</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>537.6565441070782</v>
+        <v>628.091537255048</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>70.8</v>
+        <v>391</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.08905448686362</v>
+        <v>57.23674872473266</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.01006209442952</v>
+        <v>23.37770156971532</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5002616257378371</v>
+        <v>0.4356229445051452</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2310954130951958</v>
+        <v>1.745062619666416</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6924</v>
+        <v>7799</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>535.897755021322</v>
+        <v>610.1277284248151</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.97388632108837</v>
+        <v>60.52493716677154</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.92054544231547</v>
+        <v>45.79094362880846</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8933770786292586</v>
+        <v>0.6055597024779665</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.8529674980010178</v>
+        <v>0.6062826427586856</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6925</v>
+        <v>6885</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>534.0450584473873</v>
+        <v>603.0646349000027</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>71.2</v>
+        <v>30.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>66.767250678438</v>
+        <v>61.42290319205478</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.93098688122305</v>
+        <v>54.25861054374965</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5672757818651892</v>
+        <v>0.9759503290424624</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.9259318878167528</v>
+        <v>-0.2718839591789033</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6902</v>
+        <v>6937</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>523.2366541350018</v>
+        <v>602.3105510449607</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>138</v>
+        <v>292.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.3563498249707</v>
+        <v>49.58284771223143</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.64851221138989</v>
+        <v>29.1109873064643</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.02314078435327</v>
+        <v>0.6202836648013386</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.709783457091931</v>
+        <v>-1.199343950044957</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7749</v>
+        <v>8011</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>518.091537255048</v>
+        <v>587.2042087782144</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>391</v>
+        <v>16.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.23674877699585</v>
+        <v>65.46752985945719</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.37770156303752</v>
+        <v>28.4648801133699</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4356229445051452</v>
+        <v>2.161457350250616</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.745062618553698</v>
+        <v>0.133760732463412</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7810</v>
+        <v>6916</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>511.4541579356874</v>
+        <v>571.2388901206863</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>248.5</v>
+        <v>19</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>69.71848988051464</v>
+        <v>56.66526311101158</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37.36272816139503</v>
+        <v>22.59612177253783</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9330418095833964</v>
+        <v>1.275683859519345</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.11284073240567</v>
+        <v>0.1121929304715889</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6840</v>
+        <v>7827</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>502.3119019968962</v>
+        <v>562.5201487947113</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>95</v>
+        <v>165.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.4255540315559</v>
+        <v>62.12904388681509</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.93625821604942</v>
+        <v>15.89636062858823</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4306862143443257</v>
+        <v>1.354071875855034</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.496236885465757</v>
+        <v>0.8624744037533389</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7856</v>
+        <v>6869</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>495.1969485513145</v>
+        <v>557.6565441070779</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4380</v>
+        <v>70.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.24784669575762</v>
+        <v>58.08905473508491</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.73608436993038</v>
+        <v>22.0100620472099</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.178926896721134</v>
+        <v>0.5002616257378371</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-70.50322085942679</v>
+        <v>0.2310954119824824</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7717</v>
+        <v>8016</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>493.5200993085721</v>
+        <v>552.3232707462786</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>602</v>
+        <v>289.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>62.81406924329657</v>
+        <v>52.064205947184</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.57670080488301</v>
+        <v>11.56876752757264</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9520099308572106</v>
+        <v>1.322266594723567</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.114936927606053</v>
+        <v>1.919066156368479</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6922</v>
+        <v>7610</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>491.6166916814279</v>
+        <v>545.3597406150132</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>204</v>
+        <v>1805</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.79884032727622</v>
+        <v>50.81374466307008</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.32457882317137</v>
+        <v>10.59937599806546</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8861567296719243</v>
+        <v>1.018193211932287</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4488054230392828</v>
+        <v>-7.487064552605585</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6957</v>
+        <v>7631</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>490.5426938786937</v>
+        <v>543.1792602765033</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>444</v>
+        <v>140.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>88.09248768263853</v>
+        <v>49.48927983113391</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>56.66546888005426</v>
+        <v>21.97654890154239</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.209779693106451</v>
+        <v>0.8912177429946355</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>14.18511483120432</v>
+        <v>0.3937681597927279</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7827</v>
+        <v>6840</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>487.5201487947118</v>
+        <v>542.3119019968962</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>165.5</v>
+        <v>95</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>62.12904388681509</v>
+        <v>50.42555400181282</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.89636062030135</v>
+        <v>29.93625821307651</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.354071875855034</v>
+        <v>0.4306862143443257</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.8624744037756003</v>
+        <v>-1.496236885599287</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6838</v>
+        <v>7818</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>482.214238522885</v>
+        <v>541.8748187496782</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>25.1</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.72216890037101</v>
+        <v>54.11986215375716</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33.93750998768617</v>
+        <v>15.06725915464357</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6269535727883196</v>
+        <v>0.8241990636356833</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.033039207126726</v>
+        <v>0.2296198762446157</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7556</v>
+        <v>6877</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>480.5677967067697</v>
+        <v>537.1159266505289</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>283</v>
+        <v>132.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.20017783521557</v>
+        <v>55.39477343384207</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>33.89043032508457</v>
+        <v>23.79968594412642</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.199991520531728</v>
+        <v>1.61159266505289</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>3.355133061961789</v>
+        <v>1.85213053985544</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8011</v>
+        <v>6924</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>472.2042087782157</v>
+        <v>535.897755021322</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16.9</v>
+        <v>131</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.46753014544771</v>
+        <v>51.97388635213765</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.4648801342051</v>
+        <v>29.92054544231546</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.161457350250616</v>
+        <v>0.8933770786292586</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1337607322186133</v>
+        <v>-0.8529674981568052</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7631</v>
+        <v>6925</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>468.1792602765033</v>
+        <v>534.0450584473874</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>140.5</v>
+        <v>71.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.4892799015638</v>
+        <v>66.76725078430498</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.97654881412267</v>
+        <v>38.93098691475689</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8912177429946355</v>
+        <v>0.5672757818651892</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.393768158457472</v>
+        <v>0.9259318871491252</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6916</v>
+        <v>7717</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>461.2388901206862</v>
+        <v>533.5200993085721</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19</v>
+        <v>602</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.6652634044476</v>
+        <v>62.81406924329657</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.5961217761401</v>
+        <v>19.57670080488301</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.275683859519345</v>
+        <v>0.9520099308572106</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1121929303158078</v>
+        <v>-1.114936927606053</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6907</v>
+        <v>6922</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>456.0155367021215</v>
+        <v>531.6166916814278</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.12794361400469</v>
+        <v>49.79884033279617</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.79945111060719</v>
+        <v>23.32457879349616</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4141167865530234</v>
+        <v>0.8861567296719243</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.7152200321103632</v>
+        <v>0.4488054232617973</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6909</v>
+        <v>6902</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>450.9470477296691</v>
+        <v>523.2366541350018</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>43.3</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.78264298034242</v>
+        <v>46.35634980043808</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.32701428626693</v>
+        <v>28.64851216719622</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4318729681749903</v>
+        <v>1.02314078435327</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2221356882164908</v>
+        <v>-1.709783456646838</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8033</v>
+        <v>7722</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>448.9269650575653</v>
+        <v>520.8601490958329</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>174</v>
+        <v>270</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.91559523594002</v>
+        <v>53.09868662016408</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8.61343855304162</v>
+        <v>14.92625705883575</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.203214835474138</v>
+        <v>2.554017601175977</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.9337273421062672</v>
+        <v>1.305022772158055</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7768</v>
+        <v>6907</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>437.4951236006347</v>
+        <v>496.0155367021215</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>300.5</v>
+        <v>189</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.78381906116352</v>
+        <v>51.12794361400469</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.50719337129293</v>
+        <v>17.79945111060719</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4381416956303605</v>
+        <v>0.4141167865530234</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2.216989442775475</v>
+        <v>0.7152200321103632</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8016</v>
+        <v>7856</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>437.3232707462783</v>
+        <v>495.1969485513145</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>289.5</v>
+        <v>4380</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.06420597866106</v>
+        <v>47.24784669575762</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.56876752333204</v>
+        <v>12.73608436993038</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.322266594723567</v>
+        <v>1.178926896721134</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.91906615614598</v>
+        <v>-70.50322085942679</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7818</v>
+        <v>6838</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>431.8748187496782</v>
+        <v>482.214238522885</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>61</v>
+        <v>25.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.11986205507736</v>
+        <v>56.72216886930818</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.06725913356232</v>
+        <v>33.93751003241658</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8241990636356833</v>
+        <v>0.6269535727883196</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2296198761333482</v>
+        <v>0.0330392071712312</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7822</v>
+        <v>6909</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>431.0807158995887</v>
+        <v>470.9470477296712</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>950</v>
+        <v>43.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.58542047358313</v>
+        <v>55.78264299419426</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.81499452578945</v>
+        <v>24.32701430461013</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.426256355229157</v>
+        <v>0.4318729681749903</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>10.80650354250978</v>
+        <v>0.2221356882610004</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7610</v>
+        <v>7765</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>420.359740615013</v>
+        <v>463.9143741860036</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1805</v>
+        <v>235</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.81374466254243</v>
+        <v>53.57665146223236</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.5993759971627</v>
+        <v>33.83196094006934</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.018193211932287</v>
+        <v>0.3306575827297887</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-7.487064552427547</v>
+        <v>-0.8347917653365853</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7772</v>
+        <v>6906</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>413.2166997194789</v>
+        <v>463.6222483552783</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>144.5</v>
+        <v>79.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.19697993842088</v>
+        <v>45.93817237505058</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>51.92482949087693</v>
+        <v>37.45987232383017</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7661324706770652</v>
+        <v>0.6360407123464615</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-3.237548174532485</v>
+        <v>-0.6332528368370327</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7722</v>
+        <v>7750</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>405.8601490958329</v>
+        <v>454.6245991557366</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>270</v>
+        <v>1995</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.09868656180142</v>
+        <v>46.31065249952167</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.9262570875528</v>
+        <v>17.14850779470083</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.554017601175977</v>
+        <v>0.7285012223973423</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.305022773270789</v>
+        <v>13.13327189628042</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6921</v>
+        <v>7772</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>405.8077709196656</v>
+        <v>453.2166997194788</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>144.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>11.04330268613002</v>
+        <v>49.19697995431939</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.94487407365033</v>
+        <v>51.92482951330346</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.0159805250667852</v>
+        <v>0.7661324706770652</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-3.966560313387633</v>
+        <v>-3.237548174732776</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7747</v>
+        <v>7769</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>402.6315856724973</v>
+        <v>447.2059242658773</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>111</v>
+        <v>5885</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.6540078162524</v>
+        <v>47.06263653741201</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7.941662379564302</v>
+        <v>11.72092324632662</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.06315856724972729</v>
+        <v>0.5753800060484956</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-3.162665786540892</v>
+        <v>-8.496871829857639</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6895</v>
+        <v>7747</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>390.3498241957274</v>
+        <v>442.6315856724973</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>60.25641768213963</v>
+        <v>51.65400781344772</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.10833540643277</v>
+        <v>7.941662372216042</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3627954203689726</v>
+        <v>0.06315856724972729</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.5219552884031344</v>
+        <v>-3.162665786318332</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6918</v>
+        <v>6967</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>390.2829640506146</v>
+        <v>441.8085231871884</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.24306358827986</v>
+        <v>64.23325450914048</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.93501922296836</v>
+        <v>16.72639332363772</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.428296405061464</v>
+        <v>0.8023307467979465</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.148895453204677</v>
+        <v>0.9719121704644418</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7714</v>
+        <v>8033</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>389.1067107613643</v>
+        <v>438.9269650575653</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>168.5</v>
+        <v>174</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.00906308662612</v>
+        <v>48.91559526677393</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.50414394557126</v>
+        <v>8.613438496447966</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2481086739704849</v>
+        <v>1.203214835474138</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4185287330102676</v>
+        <v>0.9337273431077132</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6877</v>
+        <v>7768</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>382.1159266505289</v>
+        <v>437.4951236006347</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>132.5</v>
+        <v>300.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.39477341041494</v>
+        <v>55.78381898937934</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.79968593631669</v>
+        <v>26.50719340225194</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.61159266505289</v>
+        <v>0.4381416956303605</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.852130540300543</v>
+        <v>2.216989443554413</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6903</v>
+        <v>7855</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>381.7249704396683</v>
+        <v>432.0522372416827</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>327</v>
+        <v>41.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>59.93195823779292</v>
+        <v>25.01158987802427</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.00251989770866</v>
+        <v>60.02808444991471</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9990188180590504</v>
+        <v>0.7635735568088405</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>3.484648664794046</v>
+        <v>0.9580013793737296</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7740</v>
+        <v>7822</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>380.4163166898917</v>
+        <v>431.0807158995885</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>108</v>
+        <v>950</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.64624735607946</v>
+        <v>55.58542044442207</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.54215480617903</v>
+        <v>19.8149945949</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.913958172032196</v>
+        <v>1.426256355229157</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.452696485104413</v>
+        <v>10.80650354206464</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7734</v>
+        <v>7714</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>377.0361037352152</v>
+        <v>429.1067107613643</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2710</v>
+        <v>168.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.37334243466317</v>
+        <v>50.00906301863061</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.24959718648316</v>
+        <v>22.50414394683881</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4547098720360912</v>
+        <v>0.2481086739704849</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>29.6846702521348</v>
+        <v>-0.4185287328990041</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7715</v>
+        <v>6903</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>376.1711075966261</v>
+        <v>421.7249704396695</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26.8</v>
+        <v>327</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.32185595108257</v>
+        <v>59.93195824214958</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24.65028271445579</v>
+        <v>17.00251981281058</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3.089793062201858</v>
+        <v>0.9990188180590504</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0393548403097833</v>
+        <v>3.484648665461676</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6863</v>
+        <v>6918</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>364.702709023983</v>
+        <v>410.2829640506146</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>96.8</v>
+        <v>73.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.45892091196277</v>
+        <v>44.24306349154698</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.93445217926407</v>
+        <v>29.9350192628186</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4141598895944894</v>
+        <v>4.428296405061464</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.691260413058032</v>
+        <v>-0.1488954532269342</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6962</v>
+        <v>6921</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>357.3538568189401</v>
+        <v>405.8077709196656</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>32.9</v>
+        <v>0</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.38090276756682</v>
+        <v>11.04330268613002</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.31375830118309</v>
+        <v>21.94487407365033</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7239395754907518</v>
+        <v>0.0159805250667852</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2558902362687414</v>
+        <v>-3.966560313387633</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7839</v>
+        <v>6965</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>357.2550947961421</v>
+        <v>393.8217358829909</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44.25</v>
+        <v>62.9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.97086616355831</v>
+        <v>32.13657444578203</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.637003603428</v>
+        <v>52.16885512768177</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5401783505942772</v>
+        <v>1.576036409864123</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1757757748894043</v>
+        <v>-0.5637851383694272</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7765</v>
+        <v>6890</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>353.9143741860036</v>
+        <v>392.6990694822978</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.57665149937635</v>
+        <v>53.16999183233575</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>33.83196094674691</v>
+        <v>10.39868015161952</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3306575827297887</v>
+        <v>2.908754350425333</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.8347917653365853</v>
+        <v>1.288399575126515</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6906</v>
+        <v>6994</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>353.6222483552783</v>
+        <v>384.9596038417694</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>79.3</v>
+        <v>30.25</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.93817253053927</v>
+        <v>47.50370490292241</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>37.45987230950873</v>
+        <v>36.13685499728647</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6360407123464615</v>
+        <v>0.5824041816094028</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,11 +4121,11 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.6332528366144947</v>
+        <v>0.6851988340401285</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>343.4597523783787</v>
+        <v>383.4597523783786</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>110.5</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.16051146281843</v>
+        <v>51.16051149899872</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8.783179220417768</v>
+        <v>8.783179051298713</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1.390399733985701</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.272473063694349</v>
+        <v>1.272473063249254</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7750</v>
+        <v>6936</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>339.6245991557366</v>
+        <v>381.9550101026432</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1995</v>
+        <v>32.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.31065251435658</v>
+        <v>52.4981433345768</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.14850779451222</v>
+        <v>17.43450550005922</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7285012223973423</v>
+        <v>2.005422817252333</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>13.13327189583542</v>
+        <v>0.0392562124561541</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6949</v>
+        <v>7740</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>334.0608900705706</v>
+        <v>380.4163166898917</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>45.3</v>
+        <v>108</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>25.73953465055843</v>
+        <v>37.64624722265943</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45.19521505440468</v>
+        <v>27.54215498877516</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2763444932548061</v>
+        <v>1.913958172032196</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>28.16144397037471</v>
+        <v>-0.4526964822113406</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6971</v>
+        <v>7839</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>331.668488303168</v>
+        <v>377.2550947961421</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>23.5</v>
+        <v>44.25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>32.44478886799249</v>
+        <v>54.97086702841518</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>29.00513087615148</v>
+        <v>28.63700358645692</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4047108907840748</v>
+        <v>0.5401783505942772</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0073331991447147</v>
+        <v>0.1757757742440313</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7547</v>
+        <v>7734</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>324.1092181187111</v>
+        <v>377.0361037352152</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>61.5</v>
+        <v>2710</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>65.69692763939274</v>
+        <v>47.37334244812129</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.39699246367637</v>
+        <v>14.24959723361065</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3109218118711062</v>
+        <v>0.4547098720360912</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.8855715127565644</v>
+        <v>29.68467024657125</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7855</v>
+        <v>7812</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>322.0522372416827</v>
+        <v>364.781738553203</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>41.9</v>
+        <v>65</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>25.01158987802427</v>
+        <v>32.78574231036802</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>60.02808444991471</v>
+        <v>21.8647559243948</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7635735568088405</v>
+        <v>0.6781738553203016</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.9580013793737296</v>
+        <v>-1.071462569789006</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6947</v>
+        <v>6863</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>313.4746358264797</v>
+        <v>364.702709023983</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.81373691648491</v>
+        <v>41.45892096733469</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.75665328925511</v>
+        <v>23.93445219923554</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.036802939801055</v>
+        <v>0.4141598895944894</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.3665048278590792</v>
+        <v>0.691260413058032</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6955</v>
+        <v>6895</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>309.674270248586</v>
+        <v>360.3498241957274</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.52396066195517</v>
+        <v>60.25641759504701</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5.700193043542666</v>
+        <v>16.10833544285274</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.1775444390343727</v>
+        <v>0.3627954203689726</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.9433535395461528</v>
+        <v>0.5219552920750985</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6967</v>
+        <v>6962</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>306.8085231871885</v>
+        <v>357.3538568189398</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>64.23325442610852</v>
+        <v>57.38090246475248</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.72639343070514</v>
+        <v>18.31375837049084</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8023307467979465</v>
+        <v>0.7239395754907518</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.9719121698079436</v>
+        <v>0.2558902365691748</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6952</v>
+        <v>6971</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>305.493221613463</v>
+        <v>351.668488303168</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>39.1</v>
+        <v>23.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.24466521357514</v>
+        <v>32.44478878774477</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.385574048176723</v>
+        <v>29.00513125753969</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.556895367473098</v>
+        <v>0.4047108907840748</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.5765980242045226</v>
+        <v>0.0073331991780943</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7689</v>
+        <v>7715</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>303.186993730072</v>
+        <v>346.1711075966259</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>157.5</v>
+        <v>26.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.09519231648637</v>
+        <v>35.32185596798705</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.14934191096033</v>
+        <v>24.65028272173035</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4899557243965188</v>
+        <v>3.089793062201858</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,11 +4704,11 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.00253271228595</v>
+        <v>0.0393548403209099</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>295.7033885353668</v>
+        <v>335.7033885353668</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>68</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.62008870389286</v>
+        <v>52.62008871546873</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8.696864545699935</v>
+        <v>8.696864515703094</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.8847199389700116</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.1876024527867</v>
+        <v>1.18760245238612</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8034</v>
+        <v>6949</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>290.5814072273635</v>
+        <v>334.0608900705706</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>19.3</v>
+        <v>45.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.18809251184884</v>
+        <v>25.73953464423805</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.67906522290632</v>
+        <v>45.19521525253562</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.995544242756206</v>
+        <v>0.2763444932548061</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.127339325806097</v>
+        <v>28.16144397037471</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7786</v>
+        <v>8032</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>288.6628729840751</v>
+        <v>324.8676913623368</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>116.5</v>
+        <v>36.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.380450564348</v>
+        <v>52.98707731282924</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.46062947625183</v>
+        <v>15.21479338371718</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4639501879994553</v>
+        <v>0.9310791340664952</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.176566472814589</v>
+        <v>0.1438934159287367</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8032</v>
+        <v>7547</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>284.867691362337</v>
+        <v>324.1092181187111</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>36.15</v>
+        <v>61.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.98707725743969</v>
+        <v>65.69692772809748</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15.2147933228207</v>
+        <v>27.39699247819382</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9310791340664952</v>
+        <v>0.3109218118711062</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1438934161290306</v>
+        <v>0.8855715109762325</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6965</v>
+        <v>7402</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>283.8217358829908</v>
+        <v>323.3424282479055</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>62.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>32.13657444578203</v>
+        <v>42.54293271745681</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>52.16885505130409</v>
+        <v>15.79453172421618</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.576036409864123</v>
+        <v>0.8436537787154206</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.563785138258158</v>
+        <v>0.2324455310488999</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6919</v>
+        <v>7705</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>283.4047313830218</v>
+        <v>321.6954573225803</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>29.75</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>34.11632168525975</v>
+        <v>41.98815956444019</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>29.0241946748545</v>
+        <v>10.25876109142788</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4097298545397143</v>
+        <v>2.000334630476201</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.4694636872054225</v>
+        <v>0.0113462765875011</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7402</v>
+        <v>6947</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>283.3424282479055</v>
+        <v>313.4746358264797</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.54293263208716</v>
+        <v>43.81373690862279</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.79453170704924</v>
+        <v>10.75665325282526</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8436537787154206</v>
+        <v>1.036802939801055</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.232445531338205</v>
+        <v>0.3665048278145728</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6910</v>
+        <v>6955</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>281.5650761406795</v>
+        <v>309.674270248586</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>25.4</v>
+        <v>93</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.39996549051856</v>
+        <v>48.52395925236974</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32.44529189548729</v>
+        <v>5.700193043149546</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3968749464426931</v>
+        <v>0.1775444390343727</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0259122475842401</v>
+        <v>0.9433535388785366</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7770</v>
+        <v>6952</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>277.9573894974026</v>
+        <v>305.493221613463</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.11619338088651</v>
+        <v>52.24466521236912</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.64688895474341</v>
+        <v>9.385573970139232</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7262472817564712</v>
+        <v>1.556895367473098</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0694205138715116</v>
+        <v>0.576598024260157</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6890</v>
+        <v>7689</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>277.6990694822986</v>
+        <v>303.186993730072</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>156</v>
+        <v>157.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.16999177240973</v>
+        <v>38.09519231648637</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.39868012924882</v>
+        <v>19.14934191096033</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.908754350425333</v>
+        <v>0.4899557243965188</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1.288399575905405</v>
+        <v>1.00253271228595</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6901</v>
+        <v>6855</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>277.5975835545717</v>
+        <v>300.9268941342152</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.15</v>
+        <v>115.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>58.28352452038468</v>
+        <v>52.68755483354919</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>24.89496289207214</v>
+        <v>8.195149809898291</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.232302261830599</v>
+        <v>0.904531456225253</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2526302202988524</v>
+        <v>5.431753391618661</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7791</v>
+        <v>7728</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>273.869178938381</v>
+        <v>296.2922566458383</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>53.8</v>
+        <v>637</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>30.69037493634044</v>
+        <v>54.09932208945909</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.5572639836166</v>
+        <v>22.12167687878262</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.831422254017748</v>
+        <v>0.3790774986708904</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0800456645870949</v>
+        <v>3.162074221042861</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6936</v>
+        <v>7791</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>271.9550101026431</v>
+        <v>293.8691789383811</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>32.2</v>
+        <v>53.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.49814335422774</v>
+        <v>30.69037443548156</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.43450545708258</v>
+        <v>21.55726387726806</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.005422817252333</v>
+        <v>1.831422254017748</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0392562124895305</v>
+        <v>-0.0800456642532742</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7812</v>
+        <v>7842</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>稜研科技*-創</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>269.781738553203</v>
+        <v>290.9699131674907</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>65</v>
+        <v>99.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>32.78574230541648</v>
+        <v>52.19186609750921</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.86475599246227</v>
+        <v>17.94037552060325</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6781738553203016</v>
+        <v>0.1039294680913178</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.071462569699999</v>
+        <v>-3.650009203771011</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7780</v>
+        <v>8034</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>267.7816980475973</v>
+        <v>290.581407227362</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>16.15</v>
+        <v>19.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.60691900418274</v>
+        <v>40.1880924025166</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.59579187521363</v>
+        <v>16.67906523024807</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.097333032294461</v>
+        <v>0.995544242756206</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0041669287308633</v>
+        <v>-0.1273393257504614</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6855</v>
+        <v>7786</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>260.9268941342152</v>
+        <v>288.6628729840751</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>52.68755482702758</v>
+        <v>44.38045051449803</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.195149869013598</v>
+        <v>11.46062947625183</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.904531456225253</v>
+        <v>0.4639501879994553</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>5.431753392286284</v>
+        <v>0.176566472814589</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7821</v>
+        <v>7780</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>258.5962155156539</v>
+        <v>287.7816980475972</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>35</v>
+        <v>16.15</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>18.90896375542165</v>
+        <v>45.60691675257713</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>36.88656174271459</v>
+        <v>19.59579181332208</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5596215515653901</v>
+        <v>1.097333032294461</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2538512743695821</v>
+        <v>0.0041669280245739</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7728</v>
+        <v>6919</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>256.2922566458381</v>
+        <v>283.4047313830218</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>637</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>54.0993221460092</v>
+        <v>34.11632208632851</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>22.12167689129513</v>
+        <v>29.02419471551326</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3790774986708904</v>
+        <v>0.4097298545397143</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>3.16207421792734</v>
+        <v>0.4694636874279609</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7842</v>
+        <v>7821</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>250.9699131674907</v>
+        <v>278.5962155156539</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>99.7</v>
+        <v>35</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.19186607971024</v>
+        <v>18.90896489398708</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.94037548598426</v>
+        <v>36.88656218184939</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1039294680913178</v>
+        <v>0.5596215515653901</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-3.650009202324491</v>
+        <v>-0.2538512741136615</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7721</v>
+        <v>7828</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>247.5489208929194</v>
+        <v>277.9152487959931</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>61.4</v>
+        <v>1800</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.51661000412044</v>
+        <v>45.08359680841307</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.47680581444355</v>
+        <v>18.28348553411428</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8867288992758168</v>
+        <v>0.6595401393057776</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1862915368237278</v>
+        <v>-27.48768676718156</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7825</v>
+        <v>6901</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>241.1112734099386</v>
+        <v>277.5975835545717</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>17.15</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.34153751950341</v>
+        <v>58.28352441162527</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.54379547154197</v>
+        <v>24.89496304229392</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2274327764295722</v>
+        <v>1.232302261830599</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.7905365524990629</v>
+        <v>0.25263022042125</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6951</v>
+        <v>7805</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>238.9237729334735</v>
+        <v>253.843575206978</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69</v>
+        <v>492.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>33.16809901090313</v>
+        <v>36.64959942320289</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>28.65591945944206</v>
+        <v>30.33009271290478</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7839551221742532</v>
+        <v>0.4992637910144471</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0321484163069443</v>
+        <v>4.141795167461211</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7828</v>
+        <v>6910</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>237.9152487959936</v>
+        <v>251.56507614068</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1800</v>
+        <v>25.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.08359688668494</v>
+        <v>48.39996569393743</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.28348547336693</v>
+        <v>32.44529193931636</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6595401393057776</v>
+        <v>0.3968749464426931</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-27.48768678075658</v>
+        <v>-0.025912247795652</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6914</v>
+        <v>7770</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>237.7468774541978</v>
+        <v>247.9573894974025</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>30.31807525315057</v>
+        <v>52.11619332429747</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>38.71739358381577</v>
+        <v>12.64688884854365</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.990107915466551</v>
+        <v>0.7262472817564712</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.7169321787062013</v>
+        <v>0.0694205140495469</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7823</v>
+        <v>7721</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>235.7075838101668</v>
+        <v>247.5489208929194</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>78.7</v>
+        <v>61.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>38.97283358167706</v>
+        <v>48.51660984285874</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.62455223814132</v>
+        <v>18.47680586536517</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4885078623151735</v>
+        <v>0.8867288992758168</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0723371853910956</v>
+        <v>0.1862915370240131</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6928</v>
+        <v>6951</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>231.2140293003883</v>
+        <v>238.9237729334737</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.88649633322137</v>
+        <v>33.16809910528907</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.92707425570182</v>
+        <v>28.65591943549496</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.09542435297685</v>
+        <v>0.7839551221742532</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.10507490544116</v>
+        <v>0.0321484161511661</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6887</v>
+        <v>6914</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>230.8435019465903</v>
+        <v>237.7468774541978</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>36.8</v>
+        <v>119</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.05606947063205</v>
+        <v>30.31807534492411</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>36.5880075959556</v>
+        <v>38.71739356543092</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7671506539903084</v>
+        <v>0.990107915466551</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.203060949658363</v>
+        <v>0.7169321784836651</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7805</v>
+        <v>7823</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>213.843575206978</v>
+        <v>235.7075838101668</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>492.5</v>
+        <v>78.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.64959952914942</v>
+        <v>38.97283358167706</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>30.33009271290478</v>
+        <v>13.62455223814132</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4992637910144471</v>
+        <v>0.4885078623151735</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>4.141795165458312</v>
+        <v>-0.0723371853910956</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7705</v>
+        <v>6928</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>211.6954573225806</v>
+        <v>231.2140293003886</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.75</v>
+        <v>45</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.98815889209168</v>
+        <v>41.88649652890738</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.25876097348154</v>
+        <v>11.92707422968127</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2.000334630476201</v>
+        <v>1.09542435297685</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0113462768768049</v>
+        <v>-0.1050749050850945</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7760</v>
+        <v>6887</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>208.9050099923977</v>
+        <v>230.8435019465904</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>32.55</v>
+        <v>36.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.22528014097103</v>
+        <v>44.05606920984054</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>26.33777197992215</v>
+        <v>36.58800756296715</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.312662736968532</v>
+        <v>0.7671506539903084</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0097167683895497</v>
+        <v>-0.2030609494358236</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7753</v>
+        <v>7704</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>206.6638199545157</v>
+        <v>227.4434820456434</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>35.5</v>
+        <v>60.6</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.59917549216678</v>
+        <v>45.43191163398793</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.94397653548293</v>
+        <v>15.16056022239729</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6738574577516532</v>
+        <v>1.085983644106159</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>2</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.08282809854049859</v>
+        <v>-0.1446034453164315</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6958</v>
+        <v>7825</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>197.5333070489489</v>
+        <v>211.1112734099386</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>16.75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.22142017876772</v>
+        <v>44.34153752673679</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>23.1364437302694</v>
+        <v>17.54379547217547</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2983429822330596</v>
+        <v>0.2274327764295722</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0545575307435594</v>
+        <v>-0.7905365524750336</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6865</v>
+        <v>7760</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>193.0700473312971</v>
+        <v>208.9050099923977</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>26.7</v>
+        <v>32.55</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.08455091655279</v>
+        <v>45.22527966184152</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.90617660044799</v>
+        <v>26.33777212404793</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3651962682742334</v>
+        <v>1.312662736968532</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.257256546698331</v>
+        <v>0.009716768890270599</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6899</v>
+        <v>6958</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>192.6984388156044</v>
+        <v>197.5333070489484</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>49.3</v>
+        <v>16.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.4668640710722</v>
+        <v>41.22142022486528</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>22.97236021361054</v>
+        <v>23.13644376852259</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.197796676910822</v>
+        <v>0.2983429822330596</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0244437186938821</v>
+        <v>-0.0545575308103243</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7769</v>
+        <v>8024</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>192.2059242658773</v>
+        <v>196.616064600724</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>5885</v>
+        <v>12.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>47.06263654065339</v>
+        <v>31.7110771507608</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.72092324077087</v>
+        <v>16.85371962642659</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5753800060484956</v>
+        <v>5.564903345936923</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-8.49687182874527</v>
+        <v>-0.0025758505569832</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>191.3377153396303</v>
+        <v>191.3377153396301</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>33.55</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.52213765731407</v>
+        <v>51.52213766073734</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>7.776681435388138</v>
+        <v>7.776681456841096</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5557130075743683</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.8033717871526205</v>
+        <v>0.8033717870969856</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.80731302281866</v>
+        <v>34.80731304532118</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.41968014362978</v>
+        <v>16.41968010457302</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.044534537242585</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1695541658590023</v>
+        <v>-0.1695541663040893</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7704</v>
+        <v>6969</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>187.4434820456434</v>
+        <v>189.7647683815922</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>60.6</v>
+        <v>30.55</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.43191181541916</v>
+        <v>42.42148649750126</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.16056018697923</v>
+        <v>12.86303121060458</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.085983644106159</v>
+        <v>0.1563524333085599</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.1446034453164315</v>
+        <v>-0.2107189423022563</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6994</v>
+        <v>6923</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>184.9596038417693</v>
+        <v>177.5137120082514</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>30.25</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>47.50370475541699</v>
+        <v>35.14603263037355</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>36.13685504611317</v>
+        <v>13.94465679323696</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5824041816094028</v>
+        <v>0.3506821724631083</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.6851988342181632</v>
+        <v>-0.2869811140583631</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6923</v>
+        <v>7753</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>177.5137120082518</v>
+        <v>176.6638199545157</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>35.14603290545219</v>
+        <v>38.59917628498732</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.94465674590008</v>
+        <v>10.94397654214765</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3506821724631083</v>
+        <v>0.6738574577516532</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,11 +6824,11 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.2869811142363992</v>
+        <v>0.08282809820668451</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.46959360849903</v>
+        <v>46.46959419994256</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.3748069620823</v>
+        <v>14.37480699338432</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.8018260099462552</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>8024</v>
+        <v>6931</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>156.6160646007241</v>
+        <v>167.3390073493419</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>12.2</v>
+        <v>38.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>31.71107730298058</v>
+        <v>31.77817158222166</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.85371946726955</v>
+        <v>12.3681633602681</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>5.564903345936923</v>
+        <v>1.012469789172174</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0025758506348748</v>
+        <v>-0.106135848099062</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6931</v>
+        <v>6865</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>147.3390073493418</v>
+        <v>163.0700473312971</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>38.1</v>
+        <v>26.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>31.77817172003144</v>
+        <v>51.08455089582315</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.36816329625734</v>
+        <v>13.90617663251539</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.012469789172174</v>
+        <v>0.3651962682742334</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1061358481658255</v>
+        <v>-0.2572565466315719</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6934</v>
+        <v>6899</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>125.2952965651404</v>
+        <v>162.6984388156049</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.84102561472672</v>
+        <v>42.46686407955733</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.584990352452</v>
+        <v>22.97236024301291</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2256093253547767</v>
+        <v>1.197796676910822</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1563645730123591</v>
+        <v>0.0244437186271224</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>118.6087208079236</v>
+        <v>138.6087208079239</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>166</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.38148180671362</v>
+        <v>39.38148171281449</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.01098942415686</v>
+        <v>17.01098943358884</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.4054070356048859</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.09398305861033179</v>
+        <v>-0.09398305838779381</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6969</v>
+        <v>6934</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>114.7647683815922</v>
+        <v>125.2952965651404</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>30.55</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>42.42148641601637</v>
+        <v>46.84103283737736</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.86303081606269</v>
+        <v>15.58499109425517</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.1563524333085599</v>
+        <v>0.2256093253547767</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.2107189420129587</v>
+        <v>-0.1563645877001868</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6908</v>
+        <v>7738</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>94.89322280318258</v>
+        <v>124.221490360591</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>26.05</v>
+        <v>158</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>25.31549887768131</v>
+        <v>42.68193342057641</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.41930629965933</v>
+        <v>16.80586243769722</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.389322280318258</v>
+        <v>0.5775818527286534</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.2500173182651242</v>
+        <v>-0.0388002737095822</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>7738</v>
+        <v>6908</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>84.22149036059088</v>
+        <v>94.89322280318258</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>158</v>
+        <v>26.05</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>42.68193345396389</v>
+        <v>25.31549886543552</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.80586239063026</v>
+        <v>17.41930629965933</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5775818527286534</v>
+        <v>1.389322280318258</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0388002731532526</v>
+        <v>-0.2500173182651242</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>74.59283710437681</v>
+        <v>94.59283710437684</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>17.5</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>33.22963210882573</v>
+        <v>33.22963220437775</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>15.88970518364658</v>
+        <v>15.88970524801041</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.9663579739844992</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.047452806811782</v>
+        <v>-0.047452806900799</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
